--- a/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
+++ b/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADDFA3C-A2D2-42E8-A432-BCCD3587282F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B52C091-D209-46C3-8E74-4088D817A829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="15645" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="11820" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="تحديث كلمات المرور" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>البريد الإلكتروني</t>
   </si>
@@ -39,7 +39,10 @@
     <t>4. لا تُنشئ العملية مستخدمين جدد؛ يجب أن يكون مستخدم Firebase Auth موجودًا.</t>
   </si>
   <si>
-    <t>m-f-elfahd@qz.org.sa</t>
+    <t>Takween@123456</t>
+  </si>
+  <si>
+    <t>students-mentor-faleh@qz.org.sa</t>
   </si>
 </sst>
 </file>
@@ -80,7 +83,7 @@
       <name val="Tajawal"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -101,6 +104,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -155,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -169,7 +178,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,11 +540,11 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="5">
-        <v>1092685119</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">

--- a/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
+++ b/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B52C091-D209-46C3-8E74-4088D817A829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A529B749-83BC-40B0-AFA9-BD78579A7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="11820" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4470" yWindow="5400" windowWidth="8220" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="تحديث كلمات المرور" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>البريد الإلكتروني</t>
   </si>
@@ -39,17 +39,14 @@
     <t>4. لا تُنشئ العملية مستخدمين جدد؛ يجب أن يكون مستخدم Firebase Auth موجودًا.</t>
   </si>
   <si>
-    <t>Takween@123456</t>
-  </si>
-  <si>
-    <t>students-mentor-faleh@qz.org.sa</t>
+    <t>r.alromi@qz.org.sa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,8 +79,13 @@
       <color theme="1"/>
       <name val="Tajawal"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tajawal"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,12 +106,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,12 +174,8 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,11 +532,11 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5" t="s">
         <v>7</v>
+      </c>
+      <c r="B2" s="6">
+        <v>1095015416</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
